--- a/agent_runs/manjidiwang/episodes/ep25/storyboard_index.xlsx
+++ b/agent_runs/manjidiwang/episodes/ep25/storyboard_index.xlsx
@@ -84,7 +84,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>接管文件签署（，总时长：12秒，镜头数：5个）</t>
+          <t>接管文件签署</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -132,7 +132,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>法务闯入（，总时长：12秒，镜头数：4个）</t>
+          <t>法务闯入</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -180,7 +180,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>对赌文件压桌（，总时长：13秒，镜头数：4个）</t>
+          <t>对赌文件压桌</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -228,7 +228,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>抵押真相摊牌（，总时长：12秒，镜头数：5个）</t>
+          <t>抵押真相摊牌</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -276,7 +276,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>鼎丰逐客（，总时长：11秒，镜头数：5个）</t>
+          <t>鼎丰逐客</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -324,7 +324,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>文件被撕碎（，总时长：12秒，镜头数：4个）</t>
+          <t>文件被撕碎</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -372,7 +372,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>龙爷杀意暴露（，总时长：13秒，镜头数：5个）</t>
+          <t>龙爷杀意暴露</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -420,7 +420,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>病房锁门查底细（，总时长：13秒，镜头数：5个）</t>
+          <t>病房锁门查底细</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -468,7 +468,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>吞并集团的诱饵（，总时长：13秒，镜头数：5个）</t>
+          <t>吞并集团的诱饵</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -516,7 +516,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>上膛后返家（，总时长：14秒，镜头数：4个）</t>
+          <t>上膛后返家</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
